--- a/allowed_users.xlsx
+++ b/allowed_users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Documents\Prashanti\Inventory Purchase Application Streamlit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D0A75-AE34-4704-A5DB-CC876F477BB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1A8E4-0A01-4587-A3AC-2BBBB8631679}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="4692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
   <si>
     <t>email</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>automation@wedtree.com</t>
+  </si>
+  <si>
+    <t>sasidhar.v@wedtree.com</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0836B3E-0865-40DC-B263-7D0CF749A9DB}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.21875" customWidth="1"/>
@@ -442,14 +445,20 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{CB5F1091-49DE-4654-A502-33DD20C314F9}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{94D2A03F-0D4E-427D-8839-D94BABE38EC4}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{42907AC0-5836-4542-AC1D-3C936D3E73A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/allowed_users.xlsx
+++ b/allowed_users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Documents\Prashanti\Inventory Purchase Application Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD1A8E4-0A01-4587-A3AC-2BBBB8631679}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D0A75-AE34-4704-A5DB-CC876F477BB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="4692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
   <si>
     <t>email</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>automation@wedtree.com</t>
-  </si>
-  <si>
-    <t>sasidhar.v@wedtree.com</t>
   </si>
 </sst>
 </file>
@@ -424,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0836B3E-0865-40DC-B263-7D0CF749A9DB}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.21875" customWidth="1"/>
@@ -445,20 +442,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{CB5F1091-49DE-4654-A502-33DD20C314F9}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{94D2A03F-0D4E-427D-8839-D94BABE38EC4}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{42907AC0-5836-4542-AC1D-3C936D3E73A3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/allowed_users.xlsx
+++ b/allowed_users.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Documents\Prashanti\Inventory Purchase Application Streamlit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajeshkannan.m\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216D0A75-AE34-4704-A5DB-CC876F477BB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3647492B-F671-4D6A-8893-04D03C1D5187}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13224" windowHeight="4692" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>email</t>
   </si>
@@ -41,6 +41,15 @@
   </si>
   <si>
     <t>automation@wedtree.com</t>
+  </si>
+  <si>
+    <t>sasidhar.v@wedtree.com</t>
+  </si>
+  <si>
+    <t>brindha@wedtree.com</t>
+  </si>
+  <si>
+    <t>anand@wedtree.com</t>
   </si>
 </sst>
 </file>
@@ -421,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0836B3E-0865-40DC-B263-7D0CF749A9DB}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.21875" customWidth="1"/>
@@ -442,14 +451,32 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{CB5F1091-49DE-4654-A502-33DD20C314F9}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{94D2A03F-0D4E-427D-8839-D94BABE38EC4}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{42907AC0-5836-4542-AC1D-3C936D3E73A3}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{4C585D14-2026-45EF-9C8F-F9FECA2ABC04}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{6A237C64-8FD0-4E70-992C-FE441DF96433}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
